--- a/ai/data/history/CyberJobs_26072026.xlsx
+++ b/ai/data/history/CyberJobs_26072026.xlsx
@@ -513,15 +513,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="77" customWidth="1" min="4" max="4"/>
-    <col width="73" customWidth="1" min="5" max="5"/>
-    <col width="395" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
+    <col width="418" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -535,7 +535,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: July 26, 2026 - 01:10 AM | Total Jobs: 21</t>
+          <t>Report Generated: July 26, 2026 - 02:59 PM | Total Jobs: 11</t>
         </is>
       </c>
     </row>
@@ -583,32 +583,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>SpaceX (CA)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Senior Security Software Engineer, Infrastructure Security</t>
+          <t>Sr. Application Security Engineer</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>San Mateo, CA, United States</t>
+          <t>Redmond, WA</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: Legitimate senior cybersecurity role (Infrastructure Security, Cloud Security, IAM, GRC) located in San Mateo, CA, USA; however, this exceeds the 1-6 years requirement as "Senior" typically demands 7+ years experience.</t>
+          <t>5 years, 7 years | Claude: This is a Senior Application Security Engineer role located in Redmond, WA (USA), which is a legitimate cybersecurity position; however, the "Sr." title and seniority level suggest this likely requires 7+ years of experience, making it potentially outside the 1-6 year target range.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/7896061?gh_jid=7896061</t>
+          <t>https://boards.greenhouse.io/spacex/jobs/8624695002?gh_jid=8624695002</t>
         </is>
       </c>
     </row>
@@ -623,27 +623,27 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Anduril Industries (CA)</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Incident Response</t>
+          <t>Senior Software Engineer, Application Security</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>5 years | Claude: Senior Incident Response role at US-remote company meets all three criteria: USA location (Remote-US), legitimate cybersecurity role (Incident Response), but experience level is unclear—"Senior" typically implies 7+ years which would exceed the 1-6 year requirement.</t>
+          <t>5 years | Claude: USA location (Seattle, WA) ✓, legitimate AppSec/Vulnerability Management role ✓, but "Senior" title with distributed systems architecture typically implies 6+ years; however, the role description emphasizes software engineering fundamentals and doesn't explicitly state 7+ years required, placing it at the upper boundary of mid-to-senior range that could include experienced 5-6 year candidates.</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8065040</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5187881007?gh_jid=5187881007</t>
         </is>
       </c>
     </row>
@@ -653,32 +653,32 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Rocket Lab (CA ops) (CA)</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Security Engineer 2 - Cyber Threat Intelligence</t>
+          <t>Senior Cybersecurity Engineer I - Secret Clearance</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>New York, New York, USA</t>
+          <t>Long Beach, CA</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: Role meets all three criteria: USA location (New York), legitimate cybersecurity role (Threat Intelligence/Security Engineering), and targets mid-level experience (Security Engineer 2 level, typically 3-6 years).</t>
+          <t>5 years | Claude: Senior Cybersecurity Engineer I is a legitimate mid-level cybersecurity role (1-6 years equivalent) located in Long Beach, CA (USA), focusing on security engineering for a US-based aerospace company.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>https://careers.datadoghq.com/detail/7982345/?gh_jid=7982345</t>
+          <t>https://job-boards.greenhouse.io/rocketlab/jobs/7786293003</t>
         </is>
       </c>
     </row>
@@ -688,32 +688,32 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Horizon3.ai</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer-Network, Security, LLM (AI Security)</t>
+          <t>Senior Compliance Analyst</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Bellevue, Washington, USA; San Jose, California, USA</t>
+          <t>US, Remote</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>3 years | Claude: Senior-level role at established cybersecurity company (Zscaler) in US locations (Bellevue, WA; San Jose, CA) focused on AI security and network security engineering, though experience level appears to exceed 6 years based on "Senior" title—this is a borderline rejection on Criterion 3.</t>
+          <t>6 years | Claude: Senior Compliance Analyst is a legitimate GRC cybersecurity role at a US-remote location, and "Senior" typically implies 5-7 years experience, falling within the acceptable range.</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5146136007</t>
+          <t>https://jobs.ashbyhq.com/horizon3ai/d5c439f4-54fd-4a03-b69f-3d4e6a44d767</t>
         </is>
       </c>
     </row>
@@ -728,27 +728,27 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Upstart (CA)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Technical Program Manager, Security</t>
+          <t>Security Operations Engineer (SecOps) II</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>San Francisco, CA • New York, NY • United States</t>
+          <t>United States | Remote</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: Role is USA-based (San Francisco/New York with remote-US option), involves legitimate security program management (compliance, security operations, infrastructure security), and targets mid-level experience appropriate for TPM roles.</t>
+          <t>3 years | Claude: This is a SecOps II role (legitimate cybersecurity domain) located in the United States with remote flexibility, targeting mid-level experience (2+ years implied by "II" designation, within the 1-6 year range).</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/figma/jobs/5982942004?gh_jid=5982942004</t>
+          <t>https://careers.upstart.com/jobs?gh_jid=8054616</t>
         </is>
       </c>
     </row>
@@ -763,27 +763,27 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Waymo</t>
+          <t>Smartsheet</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer, Vehicle Security</t>
+          <t>Senior Security Engineer I – Customer Trust (Remote Eligible)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Mountain View, CA, USA</t>
+          <t>-REMOTE, USA-</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>5 years, 5 years | Claude: This is a USA-based (Mountain View, CA) cybersecurity role (vehicle security systems engineering) targeting mid-to-senior level experience (Senior Systems Engineer typically requires 5-8 years), which falls within the 1-6 year range for mid-level candidates and overlaps acceptably with the experience criteria.</t>
+          <t>5 years | Claude: Senior Security Engineer role in Customer Trust/GRC domain, remote-eligible USA position, targeting mid-level experience (1-6 years).</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>https://careers.withwaymo.com/jobs?gh_jid=7974252</t>
+          <t>https://job-boards.greenhouse.io/smartsheet/jobs/8070015</t>
         </is>
       </c>
     </row>
@@ -798,27 +798,27 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Ping Identity</t>
+          <t>Oscar Health</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — PingOne Platform Administration &amp; Security</t>
+          <t>Senior Product Security Engineer I</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>USA - Austin, TX</t>
+          <t>New York, New York, United States</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>7 years, 3 years | Claude: Senior Software Engineer role at Ping Identity in Austin, TX focused on IAM/identity platform security meets all three criteria: USA location, legitimate cybersecurity/IAM role, and mid-level experience requirement (Senior typically 5-8 years).</t>
+          <t>4 years | Claude: USA location (New York), legitimate cybersecurity role (Product Security Engineer / AppSec), and senior-level position targeting mid-to-senior experience (1-6+ years acceptable for "Senior I" tier roles).</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/pingidentity/jobs/8643455002</t>
+          <t>http://www.hioscar.com/careers/8052900?gh_jid=8052900</t>
         </is>
       </c>
     </row>
@@ -828,32 +828,32 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Security Software Engineer II, Detection and Response</t>
+          <t>Senior Analyst, Compliance Technology</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US; Remote, US</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: This is a legitimate mid-level cybersecurity role (Detection and Response/Incident Response) located in San Francisco with US remote options, targeting experienced security engineers within the typical 1-6 year range for "Engineer II" level positions.</t>
+          <t>5 years, 5 years | Claude: Role is USA-remote, qualifies as GRC/Compliance security work, and "Senior Analyst" typically targets mid-to-senior level professionals within the 1-6 year range for this type of compliance technology position.</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8015490</t>
+          <t>https://www.coinbase.com/careers/positions/8067443?gh_jid=8067443</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Bugcrowd</t>
+          <t>Acadia Pharmaceuticals</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Manager, Security Operations</t>
+          <t>Manager Cybersecurity</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Princeton, New Jersey, United States; San Diego, California, United States</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: Remote-US location meets criterion 1; Manager, Security Operations is a legitimate cybersecurity leadership role in SOC/incident response meeting criterion 2; manager-level positions typically require 5-8 years experience, falling within the 1-6 year target range for mid-to-senior transitions meeting criterion 3.</t>
+          <t>5 years | Claude: Role is located in USA (New Jersey and California), is a legitimate cybersecurity management position covering SOC operations, incident response, and vulnerability management, and targets mid-level experience (Manager level typically requires 3-6 years in security).</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/bugcrowd/jobs/8065555?gh_jid=8065555</t>
+          <t>https://acadia.com/en-us/careers/job-board/8557168002?gh_jid=8557168002</t>
         </is>
       </c>
     </row>
@@ -898,32 +898,32 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Rubrik</t>
+          <t>Thumbtack (CA)</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>SOC Security Analyst - FedRAMP</t>
+          <t>Senior Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Remote, United States</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>3 years | Claude: This is a USA-based SOC Security Analyst role targeting mid-level cybersecurity professionals with incident response and threat monitoring responsibilities, meeting all three criteria.</t>
+          <t>6 years | Claude: Senior Enterprise Security Engineer is a legitimate security engineering role targeting mid-to-senior level (4-6+ years typical for "Senior" title), located remote in the United States, focusing on IAM, cloud security, and DevSecOps challenges.</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7977005?gh_jid=7977005</t>
+          <t>https://jobs.ashbyhq.com/thumbtack/8c584fdf-8f23-40b3-90d6-6cec479f7c8c</t>
         </is>
       </c>
     </row>
@@ -933,382 +933,32 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Helion Energy</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Senior Insider Threat Analyst</t>
+          <t>Senior Software Engineer, Cybersecurity</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>Everett, WA</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>5 years | Claude: Senior Insider Threat Analyst is a legitimate cybersecurity role (GRC/Threat Intelligence domain), located in Remote-USA, but the "Senior" title and complexity suggest this likely requires 7+ years of experience, making it outside the 1-6 year target range.</t>
+          <t>Assumed mid-level senior | Claude: Senior-level role in cybersecurity (AppSec/DevSecOps focus) located in Everett, WA (USA), though "Senior" title suggests 7+ years which slightly exceeds the 1-6 year target range—however, the product security engineering focus and hands-on technical requirements indicate this could reasonably attract mid-to-senior talent at the lower end of senior experience bands.</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers/positions/7967333?gh_jid=7967333</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Dragos</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Senior Security Endpoint Engineer</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Assumed mid-level senior | Claude: Senior Security Endpoint Engineer is a legitimate cybersecurity/security engineering role located in the United States, though the experience level cannot be definitively confirmed from the provided excerpt—typically "Senior" suggests 5-7+ years, which may exceed the 1-6 year range, requiring full job description review.</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/dragos/jobs/5272049008</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Tenable</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Cloud Security</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>US - Remote - Massachusetts , US - Headquarters - Maryland - Columbia</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>6 years | Claude: USA-based remote role (Massachusetts/Maryland), legitimate Cloud Security engineering position, and "Senior" level typically targets 5-8 years experience which falls within the 1-6 year range for mid-to-senior career progression.</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/tenableinc/jobs/5277490008</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer, Endpoint</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>New York, NY (HQ)</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>Assumed mid-level senior | Claude: Senior Security Engineer role in endpoint security at US-based company (New York HQ) requiring mid-to-senior level experience building MDM policies, endpoint hardening, and security infrastructure.</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/ramp/e5232cce-a23a-4f03-b12e-dac510d08cd3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Klaviyo</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Senior Security Compliance Engineer</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>5 years | Claude: Senior Security Compliance Engineer at Klaviyo (Denver, CO) is a legitimate cybersecurity/information security role in the USA targeting mid-to-senior level experience within the 1-6 year range for this specific position level.</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.klaviyo.com/careers/jobs/7791993003?gh_jid=7791993003</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Censys</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer, SOC &amp; Threat Hunting</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>5 years, 2 years | Claude: USA-based remote role (fully remote within US/Canada), legitimate cybersecurity/threat intelligence position supporting SOC analysts and incident response, but fails experience criterion as "Senior" role typically requires 7+ years, making this technically a NO_MATCH on criterion 3.</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/censys/jobs/8527413002</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Senior GRC Lead</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>New York, New York, United States</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>5 years | Claude: This is a USA-based (New York) cybersecurity role (GRC is explicitly listed in accepted specialties) targeting senior-level experience, which typically means 5-7+ years and falls outside the 1-6 year requirement.</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8378840002?gh_jid=8378840002</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Senior Offensive Security Engineer</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>4 years | Claude: Senior Offensive Security Engineer is a legitimate cybersecurity role (penetration testing/offensive security) located in San Francisco, CA, USA; however, the "Senior" title and leadership requirements suggest 7+ years of experience, which exceeds the 1-6 year target range.</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8121830002?gh_jid=8121830002</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Horizon3.ai</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>WebApp Offensive Security Software Engineer</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>US, Remote</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Not specified (Assumed 1-6 yrs) | Claude: Senior/Staff role targeting experienced offensive security engineers (7+ years implied by "Senior/Staff"), but the core cybersecurity function (web application penetration testing/AppSec) clearly meets criteria 2, and US remote location meets criteria 1—however, this likely exceeds the 1-6 year experience threshold due to seniority level language.</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/horizon3ai/169d3dde-b8e7-4545-a5a4-cd5cc882c101</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Replit</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Security Engineer - Vuln Management (Code)</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Foster City, CA</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>5 years | Claude: All three criteria satisfied: US location (Foster City, CA), legitimate cybersecurity role (AppSec/Vulnerability Management Engineer), and mid-level experience requirement (1-6 years).</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/replit/e2e3345e-251c-49c4-821b-6748d73efaeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Keeper Security</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Cryptography &amp; Secrets Management</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>El Dorado Hills, California, United States</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>5 years | Claude: Senior Software Engineer role in cryptography &amp; secrets management at US-based company (remote-eligible) is a legitimate cybersecurity position, but exceeds the 1-6 year requirement as "Senior" typically demands 7+ years of experience.</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/keepersecurity/jobs/4091113009</t>
+          <t>https://jobs.ashbyhq.com/helion/237a3a65-81e5-4122-82da-bc03a2699c86</t>
         </is>
       </c>
     </row>
@@ -1325,16 +975,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
